--- a/audit/qa-integral-dataset/fixtures/QA_cutover_broiler.xlsx
+++ b/audit/qa-integral-dataset/fixtures/QA_cutover_broiler.xlsx
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-18T01:14:59.161310+00:00</t>
+          <t>2026-10-18T03:03:40.476361+00:00</t>
         </is>
       </c>
     </row>

--- a/audit/qa-integral-dataset/fixtures/QA_cutover_broiler.xlsx
+++ b/audit/qa-integral-dataset/fixtures/QA_cutover_broiler.xlsx
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-18T03:03:40.476361+00:00</t>
+          <t>2026-10-23T10:13:29.967925+00:00</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1938,7 +1938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,6 +1967,11 @@
           <t>parent_code</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
